--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,26 +470,26 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>morrow batteries</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Agder</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.815542328183053, 'south': 58.43902587812143, 'north': 58.48399412187857, 'west': 8.729517671816946, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' 'eam' nan]</t>
         </is>
       </c>
     </row>
@@ -508,31 +508,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Apulia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -546,36 +546,36 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>rwe renewables europe and australia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -584,26 +584,26 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -622,26 +622,26 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>stellantis catl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -660,26 +660,26 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -698,11 +698,11 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>cellforce</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -736,11 +736,11 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -774,11 +774,11 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>leclanche</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -812,36 +812,36 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -850,11 +850,11 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>nikola</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -864,22 +864,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -888,11 +888,11 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -926,11 +926,11 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -940,22 +940,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -964,26 +964,26 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1002,36 +1002,5622 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>basquevolt</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Basque Country</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[nan 'cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[nan 'electric' 'fossil']</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fenecon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kion battery systems</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[nan 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sunrock</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>tozero</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>andrada group</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Borsod-Abaúj-Zemplén</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>basf</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>microvast gmbh</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oxford pv</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>['module']</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>svolt</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
         <v>28</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bratislava Region</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Brussels Capital</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>samsung sdi</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>seat</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Catalonia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>eve energy</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>levc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>red sun group</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>uk battery industrialisation centre</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>volklec</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>west midlands gigafactory</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>build your dreams</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Csongrád</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>amte power</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Dundee City</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sk innovation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Fejér</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Flanders</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Flanders</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>avesta battery and energy engineering</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Galați County</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>psa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Grand Est</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>levc</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Greater London</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>johnson matthey</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Greater Poland</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>audi</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Győr-Moson-Sopron</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Hajdú-Bihar</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>['fossil' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Hajdú-Bihar</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ecopro bm</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Hajdú-Bihar</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>eve energy</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hajdú-Bihar</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h tec systems</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ilika</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hampshire</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>automotive cell company</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>automotive energy supply company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>byd</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>li cycle</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>prologium</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>renault group</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>renault minth</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>toyota motor europe</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>verkor</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>akasol</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Hesse</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>['module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Knowsley</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>byd</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>huayou cobalt</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sk innovation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>volvo cars</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Košice Region</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>zhi dou</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Košice Region</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>easpring finland new materials oy</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kymenlaakso</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>finnish minerals beijing easpring</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Kymenlaakso</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>finnish minerals group</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Kymenlaakso</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>baywa re</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>lotus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Leicestershire</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>gotion high tech</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>graphenix development inc</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>['cell' nan 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>volkswagen northvolt</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lg chem</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Lower Silesia</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>lg energy solution</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Lower Silesia</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>automotive cell company</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Molise</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Nitra Region</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>freyr</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>['cell' 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>hopium</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Normandy</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>renault</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Normandy</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ego mobile</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>fraunhofer ffb</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>nextego mobile</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>primobius</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>pure battery technologies</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>rwth aachen university</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>britishvolt</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Northumberland</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>[nan 'cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>forsee power</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Nouvelle-Aquitaine</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>['module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>startec energy</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Nouvelle-Aquitaine</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>revoz</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Novo Mesto</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ox2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Opole Voivodeship</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>umicore</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Opole Voivodeship</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>finnish minerals group epsilon advanced materials</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ostrobothnia</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>freyr battery</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ostrobothnia</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>110</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>johnson matthey</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ostrobothnia</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>photovolt development partners</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>samsung sdi</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pest County</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>fiat chrysler</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>italvolt</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>micro mobility</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>northvolt south bay solutions</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pomerania</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>automotive cell company</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>e lyte</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>eberspacher</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ruse</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>svolt</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Saarland</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>basf</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Satakunta</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>blackstone technology</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>bmw</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>european semiconductor manufacturing company</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>['ingot_wafer']</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>128</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jt energy systems</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>meyer burger</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>porsche</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>131</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>amg lithium</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Saxony-Anhalt</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>133</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>battery lifecycle company</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Saxony-Anhalt</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>134</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>farasis energy</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Saxony-Anhalt</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>135</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>farasis energy europe</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Saxony-Anhalt</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>136</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>northvolt</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>137</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ecovolta</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Schwyz</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>138</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>calb</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>139</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>140</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Silesia</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>141</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>agratas</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Somerset</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>143</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>144</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>State of Berlin</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>145</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>146</v>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>nissan</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>Sunderland</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
         <is>
           <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>147</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>nissan</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>148</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>149</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>vianode</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>150</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>151</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>lion smart</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>152</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>153</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>154</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>elinor batteries</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>155</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Utena</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>156</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>['cell' nan 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>157</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>158</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>schaeffler</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Vas County</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>159</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>161</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>162</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>green cell</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Świętokrzyskie</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>midsummer</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Apulia</t>
+          <t>Andalusia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
+          <t>{'east': -5.81840517800549, 'south': 37.3004519185219, 'north': 37.4529424460031, 'west': -6.0334201245074, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -550,32 +550,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rwe renewables europe and australia</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aragon</t>
+          <t>Apulia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>rwe renewables europe and australia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stellantis catl</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -664,22 +664,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>stellantis catl</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Auvergne-Rhône-Alpes</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -702,22 +702,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cellforce</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>cellforce</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>leclanche</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>leclanche</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nikola</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -869,17 +869,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>nikola</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1006,32 +1006,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>basquevolt</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Basque Country</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[nan 'electric' 'fossil']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1120,22 +1120,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fenecon</t>
+          <t>basquevolt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Basque Country</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1158,32 +1158,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kion battery systems</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Bauska Municipality</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
+          <t>{'east': 24.543819889911187, 'south': 56.528922351248575, 'north': 56.54690964875143, 'west': 24.511190110088815, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[nan 'module_pack']</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sunrock</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'electric' 'fossil']</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tozero</t>
+          <t>fenecon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1310,22 +1310,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>andrada group</t>
+          <t>kion battery systems</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borsod-Abaúj-Zemplén</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>man</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>sunrock</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1396,22 +1396,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>tozero</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.693178009542979, 'south': 52.374616934628804, 'north': 52.56245935889386, 'west': -2.037797277763825, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1500,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>veolia</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.7518790741805517, 'south': 52.52433935124857, 'north': 52.54232664875143, 'west': -1.7814549258194483, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1538,32 +1538,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>andrada group</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Borsod-Abaúj-Zemplén</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1576,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam' 'recycling']</t>
         </is>
       </c>
     </row>
@@ -1614,32 +1614,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>microvast gmbh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1652,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>oxford pv</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -1690,22 +1690,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1728,32 +1728,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1766,32 +1766,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -1804,32 +1804,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1842,22 +1842,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1880,32 +1880,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1956,32 +1956,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1994,32 +1994,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>redux recycling</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>amte power</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2070,32 +2070,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2108,32 +2108,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>red sun group</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>uk battery industrialisation centre</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2184,32 +2184,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
+          <t>west midlands gigafactory</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2260,22 +2260,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>psa</t>
+          <t>build your dreams</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
+          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>amte power</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2308,22 +2308,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2336,22 +2336,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
+          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2374,32 +2374,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>plenitude</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>['fossil' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2450,22 +2450,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2526,32 +2526,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h tec systems</t>
+          <t>avesta battery and energy engineering</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2602,32 +2602,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ilika</t>
+          <t>psa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2640,32 +2640,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -2678,22 +2678,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -2716,32 +2716,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['fossil' nan]</t>
         </is>
       </c>
     </row>
@@ -2792,22 +2792,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2830,22 +2830,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>ecopro bm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -2868,22 +2868,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2906,32 +2906,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2944,27 +2944,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>h tec systems</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2982,22 +2982,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>ilika</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -3134,32 +3134,32 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3172,32 +3172,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3210,32 +3210,32 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3248,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3286,22 +3286,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3324,22 +3324,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3362,32 +3362,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>saft</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3476,32 +3476,32 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3514,32 +3514,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3552,32 +3552,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3590,22 +3590,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3628,32 +3628,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3666,32 +3666,32 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3704,32 +3704,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3742,22 +3742,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3780,32 +3780,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3856,22 +3856,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3894,22 +3894,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['cell' 'eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -4008,22 +4008,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>lotus</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4094,22 +4094,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4170,22 +4170,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4208,22 +4208,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4388,22 +4388,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>startec energy</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4426,32 +4426,32 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell' 'eam']</t>
         </is>
       </c>
     </row>
@@ -4502,32 +4502,32 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4540,32 +4540,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4578,22 +4578,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4616,32 +4616,32 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>ego mobile</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4654,22 +4654,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4692,32 +4692,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4730,32 +4730,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4768,32 +4768,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4806,22 +4806,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4844,32 +4844,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4882,32 +4882,32 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4920,22 +4920,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -4958,22 +4958,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>startec energy</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4996,32 +4996,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5034,32 +5034,32 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5072,22 +5072,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5262,22 +5262,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>['ingot_wafer']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5300,22 +5300,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5338,32 +5338,32 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5414,22 +5414,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5490,22 +5490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5528,22 +5528,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5566,22 +5566,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -5642,22 +5642,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5680,32 +5680,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5718,22 +5718,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5794,22 +5794,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5870,32 +5870,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5946,32 +5946,32 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -5984,32 +5984,32 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -6022,32 +6022,32 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>jt energy systems</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6098,22 +6098,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6146,22 +6146,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6212,22 +6212,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6250,22 +6250,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6288,22 +6288,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>farasis energy europe</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6326,32 +6326,32 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6364,22 +6364,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6402,32 +6402,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6440,27 +6440,27 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6488,22 +6488,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6516,22 +6516,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6554,22 +6554,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6592,30 +6592,1094 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Silesia</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>163</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>librec</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Solothurn</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>164</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>agratas</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Somerset</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>165</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>166</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>valmet automotive</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Southwest Finland</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>167</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>tesla</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>State of Berlin</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>168</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>aesc</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>169</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>nissan</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>['cell' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>170</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>nissan</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>171</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>172</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>vianode</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>173</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>174</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>lion smart</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>175</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sungeel hitech and samsung</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>176</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>177</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>178</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>elinor batteries</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>179</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ignitis renewables</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Tukums Municipality</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>180</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Utena</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>181</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>['cell' nan 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>182</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>183</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>schaeffler</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Vas County</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>184</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>185</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>186</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>187</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>188</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>189</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>190</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>green cell</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>Świętokrzyskie</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t>['module_pack']</t>
         </is>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2944,32 +2944,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h tec systems</t>
+          <t>ilika</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2982,22 +2982,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ilika</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3149,17 +3149,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>saft</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3552,22 +3552,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3742,32 +3742,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3818,32 +3818,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3932,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>lotus</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4008,22 +4008,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>electricbrands</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4213,17 +4213,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4274,22 +4274,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4388,22 +4388,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -4426,22 +4426,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'eam']</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>['cell' 'eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4540,32 +4540,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>cylib</t>
+          <t>ego mobile</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4669,17 +4669,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4707,17 +4707,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4745,17 +4745,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4844,22 +4844,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4882,22 +4882,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>startec energy</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4958,32 +4958,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>startec energy</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4996,32 +4996,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5049,17 +5049,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5072,22 +5072,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5262,32 +5262,32 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5391,17 +5391,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>fortum</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5528,22 +5528,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5566,22 +5566,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5642,32 +5642,32 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5680,32 +5680,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5718,32 +5718,32 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5756,22 +5756,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5794,22 +5794,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5832,22 +5832,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5961,17 +5961,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>jt energy systems</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>['ingot_wafer']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6037,17 +6037,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6146,22 +6146,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>farasis energy europe</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6364,22 +6364,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6402,22 +6402,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6440,27 +6440,27 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6516,22 +6516,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6554,22 +6554,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6592,32 +6592,32 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6630,22 +6630,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>librec</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6668,32 +6668,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6706,32 +6706,32 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6744,32 +6744,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6782,32 +6782,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>saietta group</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6896,32 +6896,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>vianode</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6934,32 +6934,32 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -6972,22 +6972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>lion smart</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>sungeel hitech and samsung</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7048,22 +7048,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7086,22 +7086,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>elinor batteries</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7162,32 +7162,32 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Tukums Municipality</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -7200,32 +7200,32 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>european energy</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7238,32 +7238,32 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7276,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -7314,32 +7314,32 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>schaeffler</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Vas County</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7352,22 +7352,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Viseu</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7390,22 +7390,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>london taxi company</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Warwickshire</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -7428,32 +7428,32 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>recyclus group</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Wolverhampton</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>battrion</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7504,22 +7504,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>lg energy solution derichebourg</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7542,22 +7542,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>hydrovolt</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Østfold</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7580,22 +7580,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>green cell</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Świętokrzyskie</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+          <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7604,82 +7604,6 @@
         </is>
       </c>
       <c r="H189" t="inlineStr">
-        <is>
-          <t>['recycling']</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="1" t="n">
-        <v>188</v>
-      </c>
-      <c r="B190" t="n">
-        <v>189</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>hydrovolt</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Østfold</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>['recycling']</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="n">
-        <v>189</v>
-      </c>
-      <c r="B191" t="n">
-        <v>190</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>green cell</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Świętokrzyskie</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
         <is>
           <t>['module_pack']</t>
         </is>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>ampyr solar europe</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
+          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['eam' 'recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam' 'recycling']</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>microvast gmbh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>oxford pv</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1804,32 +1804,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1880,22 +1880,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -1956,32 +1956,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1994,32 +1994,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>redux recycling</t>
+          <t>solaria</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>City state Bremen</t>
+          <t>Castille-La Mancha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
+          <t>{'east': -3.112603945216339, 'south': 40.59126757133335, 'north': 40.66597442866666, 'west': -3.2110940547836613, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2032,32 +2032,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>redux recycling</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>red sun group</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>uk battery industrialisation centre</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2260,32 +2260,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>amte power</t>
+          <t>west midlands gigafactory</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2336,32 +2336,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>build your dreams</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
+          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -2374,32 +2374,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>plenitude</t>
+          <t>amte power</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
+          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>plenitude</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2564,22 +2564,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2602,22 +2602,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>psa</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2640,32 +2640,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>avesta battery and energy engineering</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
+          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2678,32 +2678,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>holosolis</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -2716,22 +2716,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>psa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['fossil' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -2792,22 +2792,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2840,22 +2840,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['fossil' nan]</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2906,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2944,22 +2944,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ilika</t>
+          <t>ecopro bm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -2982,22 +2982,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3020,22 +3020,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3058,22 +3058,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>ilika</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>automotive energy supply company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>saft</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3552,32 +3552,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3590,32 +3590,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3628,32 +3628,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3666,22 +3666,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3704,32 +3704,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3742,22 +3742,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3818,22 +3818,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3856,32 +3856,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3894,32 +3894,32 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3932,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4008,32 +4008,32 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>electricbrands</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -4084,32 +4084,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>lotus</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4137,17 +4137,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -4274,32 +4274,32 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4388,22 +4388,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4426,22 +4426,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>['cell' 'eam']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4502,32 +4502,32 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>china three gorges corporation</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.0182480725435974, 'south': 37.899036412133896, 'north': 38.0750455878661, 'west': -1.2418359274564026, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4540,22 +4540,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>cylib</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -4578,32 +4578,32 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' 'eam']</t>
         </is>
       </c>
     </row>
@@ -4616,22 +4616,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4654,32 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>ego mobile</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4745,17 +4745,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4783,17 +4783,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4844,32 +4844,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4882,22 +4882,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4920,22 +4920,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>startec energy</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4958,32 +4958,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4996,32 +4996,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -5034,22 +5034,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -5072,22 +5072,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>startec energy</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5110,32 +5110,32 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5148,32 +5148,32 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5186,32 +5186,32 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5224,32 +5224,32 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5262,22 +5262,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5338,32 +5338,32 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5376,32 +5376,32 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5414,32 +5414,32 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>fortum</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5490,22 +5490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5528,32 +5528,32 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5566,32 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5604,22 +5604,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5642,32 +5642,32 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5680,32 +5680,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -5756,22 +5756,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5794,32 +5794,32 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5832,32 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5908,32 +5908,32 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5946,32 +5946,32 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>['ingot_wafer']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6037,17 +6037,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6108,22 +6108,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>jt energy systems</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>solarwatt</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6222,22 +6222,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6260,22 +6260,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6364,22 +6364,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6402,22 +6402,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>farasis energy europe</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6440,32 +6440,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6478,22 +6478,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>librec</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6592,22 +6592,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6630,32 +6630,32 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6668,32 +6668,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6744,22 +6744,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6820,32 +6820,32 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6858,22 +6858,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6896,32 +6896,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6934,22 +6934,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6972,22 +6972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7010,32 +7010,32 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -7048,32 +7048,32 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>saietta group</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7086,22 +7086,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>vianode</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -7162,32 +7162,32 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>lion smart</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -7200,32 +7200,32 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>sungeel hitech and samsung</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Thuringia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7276,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Trnava Region</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -7314,32 +7314,32 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>elinor batteries</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7352,32 +7352,32 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Tukums Municipality</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -7390,32 +7390,32 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>european energy</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7428,32 +7428,32 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>pv hardware</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.2753684568942568, 'south': 39.2789270927727, 'north': 39.566593819048215, 'west': -0.4325349668497363, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7466,22 +7466,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -7504,32 +7504,32 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -7542,32 +7542,32 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>hydrovolt</t>
+          <t>schaeffler</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Østfold</t>
+          <t>Vas County</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7580,30 +7580,296 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>189</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>190</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>moke international</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>{'east': -1.506328851963586, 'south': 52.27067478100342, 'north': 52.31431337031959, 'west': -1.560465821630002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>191</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>192</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>193</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>194</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>195</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
           <t>green cell</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>Świętokrzyskie</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
         <is>
           <t>['module_pack']</t>
         </is>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -550,22 +550,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>midsummer</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Apulia</t>
+          <t>Andalusia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
+          <t>{'east': -5.81840517800549, 'south': 37.3004519185219, 'north': 37.4529424460031, 'west': -6.0334201245074, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -588,32 +588,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rwe renewables europe and australia</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aragon</t>
+          <t>Apulia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>rwe renewables europe and australia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stellantis catl</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -702,22 +702,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>stellantis catl</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auvergne-Rhône-Alpes</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cellforce</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.24973504832279, 'south': 49.175654378278935, 'north': 49.20798465845837, 'west': 9.217042111389558, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leclanche</t>
+          <t>cellforce</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>leclanche</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nikola</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -945,17 +945,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>nikola</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1120,22 +1120,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>basquevolt</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Basque Country</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1158,32 +1158,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bauska Municipality</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{'east': 24.543819889911187, 'south': 56.528922351248575, 'north': 56.54690964875143, 'west': 24.511190110088815, 'accuracyLevel': 1}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>basquevolt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Basque Country</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1234,32 +1234,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Bauska Municipality</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.543819889911187, 'south': 56.528922351248575, 'north': 56.54690964875143, 'west': 24.511190110088815, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[nan 'electric' 'fossil']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fenecon</t>
+          <t>anumar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.839584444897, 'south': 47.2701236047002, 'north': 50.5642247422954, 'west': 8.97592585882661, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[nan 'module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kion battery systems</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
+          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[nan 'module_pack']</t>
+          <t>[nan 'electric' 'fossil']</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sunrock</t>
+          <t>fenecon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tozero</t>
+          <t>kion battery systems</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>man</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{'east': -1.693178009542979, 'south': 52.374616934628804, 'north': 52.56245935889386, 'west': -2.037797277763825, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1500,32 +1500,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>veolia</t>
+          <t>sunrock</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{'east': -1.7518790741805517, 'south': 52.52433935124857, 'north': 52.54232664875143, 'west': -1.7814549258194483, 'accuracyLevel': 1}</t>
+          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1538,22 +1538,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>andrada group</t>
+          <t>tozero</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borsod-Abaúj-Zemplén</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1576,32 +1576,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ampyr solar europe</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.693178009542979, 'south': 52.374616934628804, 'north': 52.56245935889386, 'west': -2.037797277763825, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1614,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>veolia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.7518790741805517, 'south': 52.52433935124857, 'north': 52.54232664875143, 'west': -1.7814549258194483, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>['eam' 'recycling']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1652,22 +1652,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>andrada group</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Borsod-Abaúj-Zemplén</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
+          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>ampyr solar europe</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
+          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam' 'recycling']</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>microvast gmbh</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>oxford pv</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -1842,22 +1842,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1880,32 +1880,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -1956,22 +1956,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>solaria</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Castille-La Mancha</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{'east': -3.112603945216339, 'south': 40.59126757133335, 'north': 40.66597442866666, 'west': -3.2110940547836613, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -2070,22 +2070,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>redux recycling</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>City state Bremen</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2108,32 +2108,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>solaria</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Castille-La Mancha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': -3.112603945216339, 'south': 40.59126757133335, 'north': 40.66597442866666, 'west': -3.2110940547836613, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>chery</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.2292197544555457, 'south': 41.31695582687022, 'north': 41.46828176513528, 'west': 2.0524698417286786, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>redux recycling</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2336,22 +2336,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>london electric vehicle company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>amte power</t>
+          <t>red sun group</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2384,22 +2384,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>uk battery industrialisation centre</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>plenitude</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>west midlands gigafactory</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -2526,32 +2526,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>build your dreams</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
+          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -2564,22 +2564,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>amte power</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2602,32 +2602,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2640,32 +2640,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
+          <t>iberdrola</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
+          <t>{'east': -4.647577390923, 'south': 37.9410260320985, 'north': 40.4866513892593, 'west': -7.54502489949799, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -2678,22 +2678,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>holosolis</t>
+          <t>plenitude</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2716,32 +2716,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>psa</t>
+          <t>sonnedix</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2754,32 +2754,32 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2792,22 +2792,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2868,22 +2868,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>['fossil' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2906,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>avesta battery and energy engineering</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
+          <t>holosolis</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module' nan]</t>
         </is>
       </c>
     </row>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>psa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3020,32 +3020,32 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3058,22 +3058,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ilika</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3096,32 +3096,32 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3134,32 +3134,32 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['fossil' nan]</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>automotive energy supply company</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3210,32 +3210,32 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>contemporary amperex technology co ltd</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3248,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>ecopro bm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3286,22 +3286,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3324,22 +3324,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3362,32 +3362,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>h tec systems</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3400,32 +3400,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>ilika</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3666,22 +3666,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -3742,32 +3742,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3818,22 +3818,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3856,32 +3856,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>saft</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3894,22 +3894,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -3970,22 +3970,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -4008,22 +4008,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4084,22 +4084,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4122,32 +4122,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>electricbrands</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4160,22 +4160,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4198,32 +4198,32 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4274,32 +4274,32 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -4426,32 +4426,32 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>lotus</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4502,32 +4502,32 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>china three gorges corporation</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>{'east': -1.0182480725435974, 'south': 37.899036412133896, 'north': 38.0750455878661, 'west': -1.2418359274564026, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4540,22 +4540,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4578,32 +4578,32 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>uniper</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.5980784945892, 'south': 51.2952318992457, 'north': 53.89231951013317, 'west': 6.653795670897641, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>['cell' 'eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4616,32 +4616,32 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -4654,22 +4654,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>cylib</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4740,22 +4740,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4768,32 +4768,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -4806,22 +4806,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -4844,32 +4844,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>solarcells</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.203308842801408, 'south': 49.56095518663227, 'north': 49.65483228015012, 'west': 6.069202658740534, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4882,22 +4882,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4920,32 +4920,32 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>china three gorges corporation</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.0182480725435974, 'south': 37.899036412133896, 'north': 38.0750455878661, 'west': -1.2418359274564026, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4958,32 +4958,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>national association of photovoltaic energy producers</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.72395043, 'south': 41.90989372, 'north': 43.314792, 'west': -2.5000827, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -4996,22 +4996,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5034,22 +5034,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['cell' 'eam']</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>startec energy</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5082,22 +5082,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5110,22 +5110,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -5148,32 +5148,32 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>b on</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.520515601962662, 'south': 50.76677643985185, 'north': 50.818131134040826, 'west': 6.451509294731699, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5224,32 +5224,32 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>deutsche post dhl</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5262,32 +5262,32 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>ego mobile</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5338,32 +5338,32 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5376,32 +5376,32 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5414,22 +5414,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5490,22 +5490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5528,32 +5528,32 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5566,32 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -5604,22 +5604,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>fortum</t>
+          <t>startec energy</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5642,32 +5642,32 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5690,22 +5690,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5718,22 +5718,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5756,22 +5756,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5794,32 +5794,32 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5832,32 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -5870,32 +5870,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5908,32 +5908,32 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5946,22 +5946,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5984,32 +5984,32 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6022,22 +6022,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6060,22 +6060,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6098,32 +6098,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>['ingot_wafer']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6136,22 +6136,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6174,32 +6174,32 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6212,32 +6212,32 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>solarwatt</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6250,32 +6250,32 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -6402,32 +6402,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6478,22 +6478,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6516,22 +6516,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6554,22 +6554,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6592,22 +6592,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6630,22 +6630,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -6668,32 +6668,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -6706,32 +6706,32 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>jt energy systems</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6744,32 +6744,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>librec</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6782,32 +6782,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>meyer burger technology ag</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -6820,32 +6820,32 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -6858,32 +6858,32 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>solarwatt</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module' nan]</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -6934,22 +6934,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6972,22 +6972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7010,32 +7010,32 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7048,32 +7048,32 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>farasis energy europe</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7086,22 +7086,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7200,22 +7200,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7276,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>galp energia</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7314,32 +7314,32 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7352,22 +7352,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>3sun</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Sicily</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7390,22 +7390,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>enel</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Sicily</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7428,22 +7428,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>pv hardware</t>
+          <t>enel green power</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Sicily</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>{'east': -0.2753684568942568, 'south': 39.2789270927727, 'north': 39.566593819048215, 'west': -0.4325349668497363, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module']</t>
         </is>
       </c>
     </row>
@@ -7466,22 +7466,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7504,22 +7504,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7542,32 +7542,32 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7580,32 +7580,32 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7618,32 +7618,32 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -7656,22 +7656,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>moke international</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>{'east': -1.506328851963586, 'south': 52.27067478100342, 'north': 52.31431337031959, 'west': -1.560465821630002, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -7732,22 +7732,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -7770,22 +7770,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7808,32 +7808,32 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>hydrovolt</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Østfold</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -7846,30 +7846,942 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>saietta group</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>196</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>nel asa</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>hydrogen</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>197</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>vianode</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>198</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>199</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>contemporary amperex technology co ltd</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>{'east': 10.987091014030122, 'south': 50.81734668405113, 'north': 50.863202198120895, 'west': 10.926428197977694, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>200</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>lion smart</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>201</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sungeel hitech and samsung</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>202</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>203</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>204</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>elinor batteries</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>205</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ignitis renewables</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Tukums Municipality</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>206</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Utena</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>207</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>pv hardware</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>{'east': -0.2753684568942568, 'south': 39.2789270927727, 'north': 39.566593819048215, 'west': -0.4325349668497363, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>208</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>['cell' nan 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>209</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>210</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>schaeffler</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Vas County</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>211</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>norsun</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>{'east': 8.251450226170956, 'south': 61.11087532060533, 'north': 61.4611983264353, 'west': 7.39511314620309, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>['polysilicon']</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>212</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>213</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>214</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>moke international</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>{'east': -1.506328851963586, 'south': 52.27067478100342, 'north': 52.31431337031959, 'west': -1.560465821630002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>215</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>216</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>217</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>218</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>219</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
           <t>green cell</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>Świętokrzyskie</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
         <is>
           <t>['module_pack']</t>
         </is>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>totalenergies</t>
+          <t>heineken espana</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,22 +588,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>midsummer</t>
+          <t>totalenergies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Apulia</t>
+          <t>Andalusia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
+          <t>{'east': -5.81840517800549, 'south': 37.3004519185219, 'north': 37.4529424460031, 'west': -6.0334201245074, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -626,32 +626,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rwe renewables europe and australia</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aragon</t>
+          <t>Apulia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.033379139941452, 'south': 41.05300731479015, 'north': 41.1697643762157, 'west': 16.730456315763153, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>rwe renewables europe and australia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stellantis catl</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>stellantis catl</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Auvergne-Rhône-Alpes</t>
+          <t>Aragon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.7344216175641901, 'south': 41.54946018702951, 'north': 41.7626684735467, 'west': -1.0202580623064157, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -778,27 +778,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baden-Wurttemberg</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{'east': 9.24973504832279, 'south': 49.175654378278935, 'north': 49.20798465845837, 'west': 9.217042111389558, 'accuracyLevel': 10}</t>
+          <t>{'east': 5.7881492792388505, 'south': 45.12702042132647, 'north': 45.23034957867353, 'west': 5.641428720761149, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cellforce</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.24973504832279, 'south': 49.175654378278935, 'north': 49.20798465845837, 'west': 9.217042111389558, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>cellforce</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>leclanche</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mercedes benz</t>
+          <t>leclanche</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.495748779339735, 'south': 47.53236022054825, 'north': 49.791477649788874, 'west': 7.511589777772395, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -983,17 +983,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nikola</t>
+          <t>mercedes benz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.292939196745259, 'south': 48.770791517534676, 'north': 48.79719309787849, 'west': 9.235018095418532, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>porsche</t>
+          <t>nikola</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.01885539100604, 'south': 48.34762002884694, 'north': 48.435137569416874, 'west': 9.920150801806425, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.236777176366996, 'south': 48.46932100420445, 'north': 48.514693930804704, 'west': 9.17915462073207, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>porsche</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.233446338611078, 'south': 48.752218519176644, 'north': 48.81079535607505, 'west': 9.134318822891228, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{'east': 9.011415273662818, 'south': 49.20001481923206, 'north': 49.21219038206837, 'west': 8.977339958881222, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.268155618579474, 'south': 48.82197615399063, 'north': 48.84174351836187, 'west': 8.242173761714762, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>basquevolt</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basque Country</t>
+          <t>Baden-Wurttemberg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.26780597566874, 'south': 49.204339253738866, 'north': 49.27661105721634, 'west': 9.177261483041761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -1234,32 +1234,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>basquevolt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bauska Municipality</t>
+          <t>Basque Country</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{'east': 24.543819889911187, 'south': 56.528922351248575, 'north': 56.54690964875143, 'west': 24.511190110088815, 'accuracyLevel': 1}</t>
+          <t>{'east': -2.584340976598566, 'south': 42.78528324285764, 'north': 42.91467931543273, 'west': -2.7610226403447933, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1272,22 +1272,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>anumar</t>
+          <t>ignitis renewables</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Bauska Municipality</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{'east': 13.839584444897, 'south': 47.2701236047002, 'north': 50.5642247422954, 'west': 8.97592585882661, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.543819889911187, 'south': 56.528922351248575, 'north': 56.54690964875143, 'west': 24.511190110088815, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>anumar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.839584444897, 'south': 47.2701236047002, 'north': 50.5642247422954, 'west': 8.97592585882661, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1363,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.188748127774693, 'south': 48.9721458805976, 'north': 49.03553344153033, 'west': 12.031620202478987, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[nan 'electric' 'fossil']</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fenecon</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.7230825332677, 'south': 48.0615537735515, 'north': 48.2481457759892, 'west': 11.360877208388, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[nan 'module_pack']</t>
+          <t>[nan 'electric' 'fossil']</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kion battery systems</t>
+          <t>fenecon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
+          <t>{'east': 13.149782339428736, 'south': 48.72576242470197, 'north': 48.73450465423967, 'west': 13.134908646027935, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>kion battery systems</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.186667201300208, 'south': 49.14334435124857, 'north': 49.16133164875143, 'west': 12.159160798699792, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[nan 'module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sunrock</t>
+          <t>man</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.152909737997533, 'south': 49.388130219286225, 'north': 49.489907458168354, 'west': 11.003700902984782, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tozero</t>
+          <t>sunrock</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.509822142415645, 'south': 48.616231407891064, 'north': 48.653452943753564, 'west': 12.457425098220062, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1576,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>tozero</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{'east': -1.693178009542979, 'south': 52.374616934628804, 'north': 52.56245935889386, 'west': -2.037797277763825, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.488435585529434, 'south': 48.2092922035092, 'north': 48.23518605203663, 'west': 11.446209039848648, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>veolia</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{'east': -1.7518790741805517, 'south': 52.52433935124857, 'north': 52.54232664875143, 'west': -1.7814549258194483, 'accuracyLevel': 1}</t>
+          <t>{'east': -1.693178009542979, 'south': 52.374616934628804, 'north': 52.56245935889386, 'west': -2.037797277763825, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>andrada group</t>
+          <t>veolia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Borsod-Abaúj-Zemplén</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.7518790741805517, 'south': 52.52433935124857, 'north': 52.54232664875143, 'west': -1.7814549258194483, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ampyr solar europe</t>
+          <t>andrada group</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Borsod-Abaúj-Zemplén</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
+          <t>{'east': 20.89551132569313, 'south': 48.05976540073172, 'north': 48.07987581070567, 'west': 20.86541015257827, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>ampyr solar europe</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1743,17 +1743,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
+          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>['eam' 'recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>microvast gmbh</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.901296152602576, 'south': 51.46525062042696, 'north': 51.48941413072069, 'west': 13.842086150846189, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['eam' 'recycling']</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>oxford pv</t>
+          <t>microvast gmbh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.281764490750414, 'south': 52.287688083123406, 'north': 52.332193534810635, 'west': 13.226551245488368, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>oxford pv</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.724256818819898, 'south': 52.31151191820719, 'north': 52.540908259189344, 'west': 12.36118008822097, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.794214460578777, 'south': 51.47071187408204, 'north': 51.505544125917964, 'west': 13.738253539421224, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -1956,32 +1956,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bratislava Region</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.830420929116917, 'south': 52.41907614825205, 'north': 52.429026843714674, 'west': 13.811741103908707, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>inobat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2032,22 +2032,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brussels Capital</t>
+          <t>Bratislava Region</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.233580736497522, 'south': 48.063676379685695, 'north': 48.2326516986113, 'west': 16.97990498127588, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Brussels Capital</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -2108,32 +2108,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>solaria</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Castille-La Mancha</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{'east': -3.112603945216339, 'south': 40.59126757133335, 'north': 40.66597442866666, 'west': -3.2110940547836613, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>chery</t>
+          <t>solaria</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Catalonia</t>
+          <t>Castille-La Mancha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{'east': 2.2292197544555457, 'south': 41.31695582687022, 'north': 41.46828176513528, 'west': 2.0524698417286786, 'accuracyLevel': 10}</t>
+          <t>{'east': -3.112603945216339, 'south': 40.59126757133335, 'north': 40.66597442866666, 'west': -3.2110940547836613, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>seat</t>
+          <t>chery</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.2292197544555457, 'south': 41.31695582687022, 'north': 41.46828176513528, 'west': 2.0524698417286786, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>redux recycling</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>City state Bremen</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2260,32 +2260,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>seat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Catalonia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 1.9587797225744947, 'south': 41.452928024079, 'north': 41.495111975921006, 'west': 1.9024602774255053, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2298,32 +2298,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>redux recycling</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>City state Bremen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.60937296635865, 'south': 53.53635233323868, 'north': 53.5682970262512, 'west': 8.564354976963706, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>london electric vehicle company</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>red sun group</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>uk battery industrialisation centre</t>
+          <t>london electric vehicle company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>volklec</t>
+          <t>red sun group</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>west midlands gigafactory</t>
+          <t>uk battery industrialisation centre</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -2526,32 +2526,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>build your dreams</t>
+          <t>volkec</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Csongrád</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>amte power</t>
+          <t>volklec</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee City</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2602,22 +2602,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>west midlands gigafactory</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -2640,32 +2640,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>iberdrola</t>
+          <t>build your dreams</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Csongrád</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{'east': -4.647577390923, 'south': 37.9410260320985, 'north': 40.4866513892593, 'west': -7.54502489949799, 'accuracyLevel': 10}</t>
+          <t>{'east': 20.22330909426438, 'south': 46.20113819361024, 'north': 46.30485801079056, 'west': 20.073169177220024, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -2678,32 +2678,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>plenitude</t>
+          <t>amte power</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Dundee City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
+          <t>{'east': -2.8888205554604, 'south': 56.451052771440395, 'north': 56.502203622052924, 'west': -3.063628673545431, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2716,32 +2716,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sonnedix</t>
+          <t>ferrari</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.885544002053798, 'south': 44.5150132707141, 'north': 44.543902086436354, 'west': 10.852853219448148, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fejér</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
+          <t>{'east': -5.518704162965421, 'south': 39.87475942385697, 'north': 39.90841057614303, 'west': -5.562573837034578, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -2792,32 +2792,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>dh2 energy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
+          <t>{'east': -4.647577390923, 'south': 37.9410260320985, 'north': 40.4866513892593, 'west': -7.54502489949799, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -2830,32 +2830,32 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>iberdrola</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -4.647577390923, 'south': 37.9410260320985, 'north': 40.4866513892593, 'west': -7.54502489949799, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -2868,32 +2868,32 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>plenitude</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flanders</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2906,32 +2906,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>avesta battery and energy engineering</t>
+          <t>sonnedix</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Galați County</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
+          <t>{'east': -6.906504870524931, 'south': 38.82802180509824, 'north': 38.92776619490176, 'west': -7.034721129475069, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>holosolis</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Fejér</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
+          <t>{'east': 18.82965134298371, 'south': 47.15034452998025, 'north': 47.16306347001974, 'west': 18.810944657016293, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>['module' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -2982,27 +2982,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>psa</t>
+          <t>besix</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grand Est</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.194347126844647, 'south': 51.321221271708545, 'north': 51.33679872829145, 'west': 3.1694128731553532, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3020,32 +3020,32 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>levc</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
+          <t>{'east': 4.377705880142278, 'south': 51.15561061103639, 'north': 51.19645270024868, 'west': 4.327958845025695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3058,32 +3058,32 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>volvo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greater Poland</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3096,27 +3096,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>audi</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3134,22 +3134,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Flanders</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.75647836186755, 'south': 51.01162024841617, 'north': 51.11020002427461, 'west': 3.6725575379308, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['fossil' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>avesta battery and energy engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Galați County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 28.13659040322077, 'south': 45.37637141544343, 'north': 45.49736858455657, 'west': 27.963969596779233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3210,32 +3210,32 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>contemporary amperex technology co ltd</t>
+          <t>holosolis</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module' nan]</t>
         </is>
       </c>
     </row>
@@ -3248,32 +3248,32 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ecopro bm</t>
+          <t>psa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.2250717049142335, 'south': 49.245202635124855, 'north': 49.247001364875146, 'west': 6.222316295085767, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3286,32 +3286,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>eve energy</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hajdú-Bihar</t>
+          <t>Grand Est</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.045007268378165, 'south': 49.05306252998049, 'north': 49.06578147001951, 'west': 7.025594731621834, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -3324,32 +3324,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>emr</t>
+          <t>levc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.2811882683122086, 'south': 51.297523767519486, 'north': 51.68293389615384, 'west': -0.4991631942360928, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3362,32 +3362,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h tec systems</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Greater Poland</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.31134567808409, 'south': 52.186574946260684, 'north': 52.26019113399743, 'west': 18.191072839982315, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3400,32 +3400,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ilika</t>
+          <t>audi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.704271559231216, 'south': 47.63681673430533, 'north': 47.72984776037434, 'west': 17.56596159506566, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3438,32 +3438,32 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['fossil' nan]</t>
         </is>
       </c>
     </row>
@@ -3476,22 +3476,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>catl</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -3514,32 +3514,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>contemporary amperex technology co ltd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3552,22 +3552,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>eramet suez</t>
+          <t>ecopro bm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3590,22 +3590,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>eve energy</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hajdú-Bihar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.71086564133211, 'south': 47.47338149450944, 'north': 47.58995250549056, 'west': 21.53802235866789, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>prologium</t>
+          <t>emr</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3666,32 +3666,32 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>h tec systems</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3704,32 +3704,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>hamburg green hydrogen hub</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -3742,22 +3742,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>ilika</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hauts-de-France</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.449094865107286, 'south': 50.980418567607344, 'north': 51.008842561168144, 'west': -1.508401206810452, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>renault group</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>renault minth</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>saft</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.121182808680378, 'south': 49.40413017562429, 'north': 49.41312382437572, 'west': 2.107359191319622, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>toyota motor europe</t>
+          <t>eramet suez</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>verkor</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.9282400719596318, 'south': 50.431512720797635, 'north': 50.461341279202365, 'west': 2.8813839280403686, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -3970,22 +3970,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>akasol</t>
+          <t>prologium</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4008,22 +4008,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>glencore britishvolt</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -4046,22 +4046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Knowsley</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4084,32 +4084,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>byd</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4122,32 +4122,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>huayou cobalt</t>
+          <t>renault group</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.122708534247327, 'south': 50.34297071284946, 'north': 50.398411287150545, 'west': 3.035735465752673, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4160,22 +4160,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sk innovation</t>
+          <t>renault minth</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Komárom-Esztergom</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.5958222612039354, 'south': 50.46193117562429, 'north': 50.470924824375714, 'west': 2.581691738796065, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4198,32 +4198,32 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>volvo cars</t>
+          <t>saft</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.844677657505151, 'south': 50.50016935124857, 'north': 50.51815664875143, 'west': 2.816388342494849, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4236,22 +4236,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>zhi dou</t>
+          <t>toyota motor europe</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Košice Region</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
+          <t>{'east': 3.5679556995225914, 'south': 50.33173888518208, 'north': 50.38644511481792, 'west': 3.482156300477409, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4274,22 +4274,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>easpring finland new materials oy</t>
+          <t>verkor</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hauts-de-France</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 2.431777535628651, 'south': 50.99985923656883, 'north': 51.068940763431165, 'west': 2.3218424643713487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>finnish minerals beijing easpring</t>
+          <t>akasol</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.686620210377718, 'south': 49.84474495759695, 'north': 49.899698335693174, 'west': 8.615127588265333, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -4350,22 +4350,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>finnish minerals group</t>
+          <t>glencore britishvolt</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kymenlaakso</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.3613610796854584, 'south': 51.417670417209834, 'north': 51.46163963815849, 'west': 0.31142776951638473, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -4388,32 +4388,32 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>baywa re</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Knowsley</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
+          <t>{'east': -2.7848325756101486, 'south': 53.346631287550544, 'north': 53.3820389197578, 'west': -2.8562320000766497, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4426,22 +4426,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>lotus</t>
+          <t>byd</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>electricbrands</t>
+          <t>huayou cobalt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.02626000679121, 'south': 47.70225879501302, 'north': 47.722369204986975, 'west': 17.99636599320879, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>gotion high tech</t>
+          <t>sk innovation</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Komárom-Esztergom</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4540,32 +4540,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>graphenix development inc</t>
+          <t>volvo cars</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -4578,32 +4578,32 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>uniper</t>
+          <t>zhi dou</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Košice Region</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>{'east': 11.5980784945892, 'south': 51.2952318992457, 'north': 53.89231951013317, 'west': 6.653795670897641, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.352141564262467, 'south': 48.651961553575575, 'north': 48.775930446424425, 'west': 21.164026435737533, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4616,22 +4616,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>easpring finland new materials oy</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4654,32 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>finnish minerals beijing easpring</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4692,22 +4692,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>volkswagen group components</t>
+          <t>finnish minerals group</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Kymenlaakso</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 27.007073004073145, 'south': 60.43623438503798, 'north': 60.49656561496202, 'west': 26.884566995926857, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -4730,32 +4730,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>volkswagen northvolt</t>
+          <t>baywa re</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lower Saxony</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.768207246122227, 'south': 42.237743552077085, 'north': 42.25745641692802, 'west': 11.740996804661673, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -4768,32 +4768,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>lg chem</t>
+          <t>lotus</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
+          <t>{'east': -1.185206456727828, 'south': 52.54100635124824, 'north': 52.55899364875175, 'west': -1.214793543272172, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4806,32 +4806,32 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>lg energy solution</t>
+          <t>polytechnic university of milan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lower Silesia</t>
+          <t>Lombardy</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.277930280126062, 'south': 45.39217387866174, 'north': 45.535977599221184, 'west': 9.06591510184385, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4844,32 +4844,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>solarcells</t>
+          <t>electricbrands</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>{'east': 6.203308842801408, 'south': 49.56095518663227, 'north': 49.65483228015012, 'west': 6.069202658740534, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.979687279962073, 'south': 51.505687276390006, 'north': 51.577160792979065, 'west': 9.878951301731295, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -4882,32 +4882,32 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>enova value</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.5980784945892, 'south': 51.2952318992457, 'north': 53.89231951013317, 'west': 6.653795670897641, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -4920,32 +4920,32 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>china three gorges corporation</t>
+          <t>gotion high tech</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>{'east': -1.0182480725435974, 'south': 37.899036412133896, 'north': 38.0750455878661, 'west': -1.2418359274564026, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -4958,32 +4958,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>national association of photovoltaic energy producers</t>
+          <t>graphenix development inc</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>{'east': -0.72395043, 'south': 41.90989372, 'north': 43.314792, 'west': -2.5000827, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.39737487771509, 'south': 51.65144861839693, 'north': 51.66817163652086, 'west': 9.378799354242966, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -4996,32 +4996,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>uniper</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nitra Region</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.5980784945892, 'south': 51.2952318992457, 'north': 53.89231951013317, 'west': 6.653795670897641, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5034,22 +5034,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>freyr</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nordland</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>['cell' 'eam']</t>
+          <t>['cell' nan 'eam']</t>
         </is>
       </c>
     </row>
@@ -5072,22 +5072,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>hopium</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5110,32 +5110,32 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>renault</t>
+          <t>volkswagen group components</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Normandy</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>b on</t>
+          <t>volkswagen northvolt</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Saxony</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>{'east': 6.520515601962662, 'south': 50.76677643985185, 'north': 50.818131134040826, 'west': 6.451509294731699, 'accuracyLevel': 10}</t>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>cylib</t>
+          <t>lg chem</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 16.942223164653207, 'south': 50.966038519670285, 'north': 50.97503216842171, 'west': 16.927939799213995, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'cell']</t>
         </is>
       </c>
     </row>
@@ -5224,32 +5224,32 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>deutsche post dhl</t>
+          <t>lg energy solution</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Lower Silesia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5262,32 +5262,32 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ego mobile</t>
+          <t>solarcells</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.203308842801408, 'south': 49.56095518663227, 'north': 49.65483228015012, 'west': 6.069202658740534, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>impact clean power technology</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Mazovia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.2711512942955, 'south': 52.0978496125492, 'north': 52.368153944595, 'west': 20.8516883368428, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5338,22 +5338,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>fraunhofer ffb</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.02515803802899, 'south': 41.96664218357598, 'north': 42.006732149173125, 'west': 14.964670874620774, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5376,32 +5376,32 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>nextego mobile</t>
+          <t>china three gorges corporation</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.0182480725435974, 'south': 37.899036412133896, 'north': 38.0750455878661, 'west': -1.2418359274564026, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5414,22 +5414,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>primobius</t>
+          <t>hyundai mobis</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.72395043, 'south': 41.90989372, 'north': 43.314792, 'west': -2.5000827, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -5452,32 +5452,32 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>pure battery technologies</t>
+          <t>mcpv</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.72395043, 'south': 41.90989372, 'north': 43.314792, 'west': -2.5000827, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -5490,32 +5490,32 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>rwth aachen university</t>
+          <t>national association of photovoltaic energy producers</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.72395043, 'south': 41.90989372, 'north': 43.314792, 'west': -2.5000827, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -5528,22 +5528,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>britishvolt</t>
+          <t>gotion inobat batteries</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Northumberland</t>
+          <t>Nitra Region</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.203510679385108, 'south': 48.073414059960506, 'north': 48.09885194003949, 'west': 18.165421320614893, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[nan 'cell' 'module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -5566,22 +5566,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>forsee power</t>
+          <t>freyr</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Nordland</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.533365159661637, 'south': 66.09555949009953, 'north': 66.78387692349938, 'west': 13.188270357919233, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['cell' 'eam']</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>startec energy</t>
+          <t>hopium</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5614,22 +5614,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Nouvelle-Aquitaine</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
+          <t>{'east': 1.4948061634798788, 'south': 49.07231096191137, 'north': 49.113525038088625, 'west': 1.4318418365201213, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5642,22 +5642,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>revoz</t>
+          <t>renault</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Novo Mesto</t>
+          <t>Normandy</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
+          <t>{'east': 0.31886377737636096, 'south': 49.496896635124855, 'north': 49.49869536487515, 'west': 0.31609422262363907, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -5680,32 +5680,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ox2</t>
+          <t>b on</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.520515601962662, 'south': 50.76677643985185, 'north': 50.818131134040826, 'west': 6.451509294731699, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5718,22 +5718,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>umicore</t>
+          <t>cylib</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Opole Voivodeship</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -5756,32 +5756,32 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>finnish minerals group epsilon advanced materials</t>
+          <t>deutsche post dhl</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5794,32 +5794,32 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>freyr battery</t>
+          <t>ego mobile</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5832,32 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>johnson matthey</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ostrobothnia</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
+          <t>{'east': 6.972890903720807, 'south': 50.915449013912095, 'north': 50.959219025077154, 'west': 6.927985101565835, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -5870,32 +5870,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>fraunhofer ffb</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -5908,32 +5908,32 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>photovolt development partners</t>
+          <t>nextego mobile</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -5946,22 +5946,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>samsung sdi</t>
+          <t>primobius</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Pest County</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
+          <t>{'east': 8.129861195726217, 'south': 50.98693272272397, 'north': 51.005533364701684, 'west': 8.079254137532761, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -5984,32 +5984,32 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>fiat chrysler</t>
+          <t>pure battery technologies</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.522725596119567, 'south': 51.34688986944242, 'north': 51.38640297699042, 'west': 7.436713019019417, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6022,22 +6022,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>italvolt</t>
+          <t>rwth aachen university</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6060,22 +6060,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>micro mobility</t>
+          <t>triwo ag</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>North Rhine-Westphalia</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6098,32 +6098,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>britishvolt</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Piedmont</t>
+          <t>Northumberland</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.486521581294416, 'south': 55.101808476974824, 'north': 55.148760091061156, 'west': -1.567174610804679, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'cell' 'module_pack']</t>
         </is>
       </c>
     </row>
@@ -6136,22 +6136,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>fortum</t>
+          <t>forsee power</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': 0.39865002888651413, 'south': 46.54472008430518, 'north': 46.62050191569482, 'west': 0.2883139711134859, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6174,22 +6174,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>fortum battery recycling</t>
+          <t>startec energy</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pirkanmaa</t>
+          <t>Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
+          <t>{'east': -0.42813963484333717, 'south': 44.84478552998026, 'north': 44.85750447001975, 'west': -0.4460823651566629, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6212,32 +6212,32 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>revoz</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Novo Mesto</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 15.211923613302544, 'south': 45.76816350041924, 'north': 45.84600721181288, 'west': 15.125180545809764, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>['module_pack' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>northvolt south bay solutions</t>
+          <t>ox2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6260,22 +6260,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Pomerania</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
+          <t>{'east': 17.635182972509067, 'south': 50.63194886119511, 'north': 50.652059271169065, 'west': 17.603464488428433, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -6288,22 +6288,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>automotive cell company</t>
+          <t>umicore</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Opole Voivodeship</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 17.378517288819175, 'south': 50.44570251161992, 'north': 50.501867830070886, 'west': 17.290214400634028, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6326,22 +6326,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>e lyte</t>
+          <t>finnish minerals group epsilon advanced materials</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6364,32 +6364,32 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>sng solar</t>
+          <t>freyr battery</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6402,32 +6402,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>eberspacher</t>
+          <t>johnson matthey</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ruse</t>
+          <t>Ostrobothnia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.69022613548251, 'south': 63.06235015650488, 'north': 63.12965246107453, 'west': 21.541318359146487, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -6440,32 +6440,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>svolt</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Saarland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.177081863538468, 'south': 51.710079613642115, 'north': 51.796840007641904, 'west': -1.319509894915436, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -6478,32 +6478,32 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>li cycle glencore</t>
+          <t>photovolt development partners</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sardinia</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
+          <t>{'east': -0.8700660028834721, 'south': 51.459409373196955, 'north': 52.16846751466819, 'west': -1.7195007584303506, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -6516,22 +6516,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>basf</t>
+          <t>samsung sdi</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Satakunta</t>
+          <t>Pest County</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.158261729415546, 'south': 47.66702746913661, 'north': 47.69945453086339, 'west': 19.11008027058445, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -6554,32 +6554,32 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>blackstone technology</t>
+          <t>fiat chrysler</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6592,22 +6592,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>italvolt</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.844896013549455, 'south': 45.38066742905088, 'north': 45.388755825588596, 'west': 7.836848508602034, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -6630,22 +6630,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>micro mobility</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['electric']</t>
         </is>
       </c>
     </row>
@@ -6668,32 +6668,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>european semiconductor manufacturing company</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Piedmont</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.762857702337489, 'south': 45.00679706738262, 'north': 45.13352365046831, 'west': 7.5778599181360695, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>['ingot_wafer']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>jt energy systems</t>
+          <t>fortum</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6744,32 +6744,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>meyer burger</t>
+          <t>fortum battery recycling</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pirkanmaa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>{'east': 12.86416539007656, 'south': 50.69177535124857, 'north': 50.70976264875143, 'west': 12.835760609923442, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.089090641514456, 'south': 61.758494786671086, 'north': 61.7805246370387, 'west': 23.042501155360544, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -6782,32 +6782,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>meyer burger technology ag</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6820,32 +6820,32 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>midsummer</t>
+          <t>northvolt south bay solutions</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Pomerania</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 18.800645169287666, 'south': 54.26415059853274, 'north': 54.44038940146726, 'west': 18.497594830712334, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>['module']</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>solarwatt</t>
+          <t>automotive cell company</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>['module' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>e lyte</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6906,22 +6906,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Saxony</t>
+          <t>Rheinland-Pfalz</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.846920817292972, 'south': 49.41912208001153, 'north': 49.45860979846688, 'west': 7.6563392399020875, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -6934,32 +6934,32 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>amg lithium</t>
+          <t>sng solar</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 24.311465500035062, 'south': 56.83421483411752, 'north': 57.05779339669368, 'west': 23.900318862757935, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['deployment']</t>
         </is>
       </c>
     </row>
@@ -6972,27 +6972,27 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>battery lifecycle company</t>
+          <t>eberspacher</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Ruse</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 26.46456200000006, 'south': 43.314156000000054, 'north': 44.03866720000011, 'west': 25.45826200000009, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>farasis energy</t>
+          <t>svolt</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saarland</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 6.712134539665601, 'south': 49.23040732223842, 'north': 49.248954527013105, 'west': 6.689386163775832, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7048,22 +7048,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>farasis energy europe</t>
+          <t>li cycle glencore</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Sardinia</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.82842015716897, 'south': 38.8591910527341, 'north': 41.3133205526259, 'west': 8.13072799347893, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7086,22 +7086,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>li cycle</t>
+          <t>basf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Satakunta</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
+          <t>{'east': 22.15629064481865, 'south': 61.30565177481619, 'north': 61.32768162518381, 'west': 22.11037595518135, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>norcsi</t>
+          <t>blackstone technology</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Saxony-Anhalt</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.170802679046409, 'south': 51.11103302752995, 'north': 51.142678785040744, 'west': 13.087836468078457, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>northvolt</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -7200,32 +7200,32 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ecovolta</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Schwyz</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -7238,32 +7238,32 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>calb</t>
+          <t>european semiconductor manufacturing company</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7276,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>galp energia</t>
+          <t>jt energy systems</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -7314,27 +7314,27 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>mercedes benz energy</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Setúbal</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
+          <t>{'east': 14.133282026741975, 'south': 51.25923519306523, 'north': 51.29309244289519, 'west': 14.077890184433112, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7352,22 +7352,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3sun</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sicily</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.377158995430786, 'south': 50.89650634923862, 'north': 50.93969230494892, 'west': 13.311327599881487, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module' 'cell']</t>
         </is>
       </c>
     </row>
@@ -7390,22 +7390,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>enel</t>
+          <t>midsummer</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sicily</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -7428,22 +7428,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>enel green power</t>
+          <t>solarwatt</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sicily</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>['cell' 'module']</t>
+          <t>['module' nan]</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ae elemental</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saxony</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.550681217373935, 'south': 50.69208436668295, 'north': 50.7538028554246, 'west': 12.431212728003908, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'electric']</t>
         </is>
       </c>
     </row>
@@ -7504,32 +7504,32 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>amg lithium</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Silesia</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -7542,22 +7542,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>librec</t>
+          <t>battery lifecycle company</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Solothurn</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7580,22 +7580,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>agratas</t>
+          <t>farasis energy</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7618,22 +7618,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>farasis energy europe</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -7656,32 +7656,32 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>valmet automotive</t>
+          <t>li cycle</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Southwest Finland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
+          <t>{'east': 11.666155627612763, 'south': 52.11302392312941, 'north': 52.16994742032871, 'west': 11.572401049348347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>meyer burger</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -7704,22 +7704,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>State of Berlin</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['module']</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7732,32 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>aesc</t>
+          <t>nexwafe</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.351755668282912, 'south': 51.6050106188674, 'north': 51.64429590459737, 'west': 12.282901278442232, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack' nan]</t>
+          <t>['ingot_wafer']</t>
         </is>
       </c>
     </row>
@@ -7770,22 +7770,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>norcsi</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Saxony-Anhalt</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 12.007894073905979, 'south': 51.46824374507202, 'north': 51.4972081039573, 'west': 11.955331565791347, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>['cell' nan]</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -7808,32 +7808,32 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>northvolt</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Schleswig-Holstein</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 9.138809415376675, 'south': 54.17658006003535, 'north': 54.21275817621844, 'west': 9.072678883413348, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -7846,27 +7846,27 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>saietta group</t>
+          <t>ecovolta</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Schwyz</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+          <t>{'east': 8.665515373442128, 'south': 47.014318672227304, 'north': 47.03028574910165, 'west': 8.63886730772937, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -7884,32 +7884,32 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>nel asa</t>
+          <t>calb</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>hydrogen</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['cell' 'module_pack' 'eam']</t>
         </is>
       </c>
     </row>
@@ -7922,32 +7922,32 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>vianode</t>
+          <t>fusion fuel green</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Telemark</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>['eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7960,32 +7960,32 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>catl</t>
+          <t>galp energia</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.681435537087584, 'south': 37.865777084375594, 'north': 38.04929489872405, 'west': -8.890550901882476, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[nan 'cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -7998,32 +7998,32 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>contemporary amperex technology co ltd</t>
+          <t>hyperion renewables</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>{'east': 10.987091014030122, 'south': 50.81734668405113, 'north': 50.863202198120895, 'west': 10.926428197977694, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.831551878770371, 'south': 38.48011000570002, 'north': 38.56868717337212, 'west': -8.944842011610488, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8036,32 +8036,32 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>lion smart</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Setúbal</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+          <t>{'east': -8.879729959021228, 'south': 38.55219542385758, 'north': 38.585846576142416, 'west': -8.922780040978774, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>['module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8074,32 +8074,32 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>sungeel hitech and samsung</t>
+          <t>enel</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Thuringia</t>
+          <t>Sicily</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+          <t>{'east': 15.126079696322765, 'south': 37.42048193336457, 'north': 37.56080338946649, 'west': 15.02875415076176, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan 'module' 'cell']</t>
         </is>
       </c>
     </row>
@@ -8112,22 +8112,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>gotion inobat batteries</t>
+          <t>ae elemental</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.46370186425747, 'south': 50.45782940973647, 'north': 50.51748652654593, 'west': 19.36987815283233, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -8150,32 +8150,32 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>inobat</t>
+          <t>stellantis</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Trnava Region</t>
+          <t>Silesia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+          <t>{'east': 19.03939220706789, 'south': 50.090434630251295, 'north': 50.1838993697487, 'west': 18.89342779293211, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>['cell' 'module_pack']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8188,22 +8188,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>elinor batteries</t>
+          <t>librec</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Trøndelag</t>
+          <t>Solothurn</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+          <t>{'east': 7.576800610512958, 'south': 47.17046994348771, 'north': 47.19454268087654, 'west': 7.54760484225659, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>['cell']</t>
+          <t>['recycling']</t>
         </is>
       </c>
     </row>
@@ -8226,32 +8226,32 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ignitis renewables</t>
+          <t>agratas</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Tukums Municipality</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+          <t>{'east': -2.966574158866892, 'south': 51.09991785910348, 'north': 51.16072612199926, 'west': -3.040637001994926, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>['deployment']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -8264,27 +8264,27 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>european energy</t>
+          <t>gasunie</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>South Holland</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.642246900432829, 'south': 51.82214925573732, 'north': 52.022850744262676, 'west': 4.316087099567172, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -8302,27 +8302,27 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>pv hardware</t>
+          <t>hycc</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>South Holland</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>{'east': -0.2753684568942568, 'south': 39.2789270927727, 'north': 39.566593819048215, 'west': -0.4325349668497363, 'accuracyLevel': 10}</t>
+          <t>{'east': 4.642246900432829, 'south': 51.82214925573732, 'north': 52.022850744262676, 'west': 4.316087099567172, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -8340,32 +8340,32 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>royal dutch shell</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>South Holland</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.642246900432829, 'south': 51.82214925573732, 'north': 52.022850744262676, 'west': 4.316087099567172, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>['cell' nan 'eam']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8378,32 +8378,32 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>uniper</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>South Holland</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+          <t>{'east': 4.642246900432829, 'south': 51.82214925573732, 'north': 52.022850744262676, 'west': 4.316087099567172, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8416,32 +8416,32 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>schaeffler</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vas County</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+          <t>{'east': 23.17405173521075, 'south': 60.36322289002605, 'north': 60.40344370997394, 'west': 23.09261486478925, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>[nan]</t>
+          <t>['module_pack']</t>
         </is>
       </c>
     </row>
@@ -8454,32 +8454,32 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>norsun</t>
+          <t>valmet automotive</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vestland</t>
+          <t>Southwest Finland</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>{'east': 8.251450226170956, 'south': 61.11087532060533, 'north': 61.4611983264353, 'west': 7.39511314620309, 'accuracyLevel': 10}</t>
+          <t>{'east': 21.44165659811968, 'south': 60.78421721753881, 'north': 60.81664427926559, 'west': 21.37515400979052, 'accuracyLevel': 2}</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>['polysilicon']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -8492,22 +8492,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>stellantis</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>State of Berlin</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>[nan 'electric']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>london taxi company</t>
+          <t>aesc</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8540,22 +8540,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>['electric' nan]</t>
+          <t>['cell' 'module_pack' nan]</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>moke international</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -8578,22 +8578,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Warwickshire</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>{'east': -1.506328851963586, 'south': 52.27067478100342, 'north': 52.31431337031959, 'west': -1.560465821630002, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>['electric']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>recyclus group</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -8616,22 +8616,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Wolverhampton</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['electric' nan]</t>
         </is>
       </c>
     </row>
@@ -8644,27 +8644,27 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>battrion</t>
+          <t>saietta group</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -8682,32 +8682,32 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>lg energy solution derichebourg</t>
+          <t>nel asa</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>hydrogen</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>[nan]</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>hydrovolt</t>
+          <t>vianode</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Østfold</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+          <t>{'east': 9.650593931856756, 'south': 59.11056163512485, 'north': 59.112360364875144, 'west': 9.647090068143244, 'accuracyLevel': 1}</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>['recycling']</t>
+          <t>['eam']</t>
         </is>
       </c>
     </row>
@@ -8758,30 +8758,828 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>catl</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>{'east': 11.042818518511504, 'south': 50.96796336832227, 'north': 50.98661954344408, 'west': 11.012904147220443, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>[nan 'cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>220</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>contemporary amperex technology co ltd</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>{'east': 10.987091014030122, 'south': 50.81734668405113, 'north': 50.863202198120895, 'west': 10.926428197977694, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>221</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>lion smart</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>{'east': 10.75616528468898, 'south': 50.4175597443067, 'north': 50.43717896182797, 'west': 10.710515273546633, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>['module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>222</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>sungeel hitech and samsung</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Thuringia</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>{'east': 12.1244000937386, 'south': 50.82512988478043, 'north': 50.9200134673793, 'west': 12.043412258178638, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>223</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>gotion inobat batteries</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>224</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>inobat</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Trnava Region</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>{'east': 17.566157352814365, 'south': 48.27251017562412, 'north': 48.281503824375875, 'west': 17.552642647185635, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>['cell' 'module_pack']</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>225</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>elinor batteries</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>{'east': 10.0138512334075, 'south': 62.8904313423315, 'north': 63.6465504546332, 'west': 9.17706499974905, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>['cell']</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>226</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ignitis renewables</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Tukums Municipality</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>{'east': 23.10391894070486, 'south': 56.92760035124857, 'north': 56.94558764875143, 'west': 23.07094105929514, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>['deployment']</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>227</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>european energy</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Utena</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>{'east': 25.12512133757019, 'south': 55.5128509433159, 'north': 55.53828882339488, 'west': 25.08016659577942, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>228</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>pv hardware</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>{'east': -0.2753684568942568, 'south': 39.2789270927727, 'north': 39.566593819048215, 'west': -0.4325349668497363, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>229</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>['cell' nan 'eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>230</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>volkswagen</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>{'east': -0.2233115815890593, 'south': 39.6499839578681, 'north': 39.7166826421319, 'west': -0.3100218184109407, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>231</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>schaeffler</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Vas County</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>{'east': 16.67497971157691, 'south': 47.19462165724717, 'north': 47.267130771578834, 'west': 16.568125699952688, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>[nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>232</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>norsun</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>{'east': 8.251450226170956, 'south': 61.11087532060533, 'north': 61.4611983264353, 'west': 7.39511314620309, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>['polysilicon']</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>233</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>stellantis</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Viseu</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>{'east': -7.745476611297256, 'south': 40.59235052101233, 'north': 40.61614547898767, 'west': -7.776823388702743, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>[nan 'electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>234</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>london taxi company</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>{'east': -1.4019123625614562, 'south': 52.42433965124857, 'north': 52.44232694875143, 'west': -1.4314210374385437, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>['electric' nan]</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>235</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>moke international</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>{'east': -1.506328851963586, 'south': 52.27067478100342, 'north': 52.31431337031959, 'west': -1.560465821630002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>['electric']</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>236</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>recyclus group</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>{'east': -2.047589062994391, 'south': 52.543274219952295, 'north': 52.64243985317021, 'west': -2.208067813103782, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>237</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>battrion</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>{'east': 8.651844002323093, 'south': 47.38425215646728, 'north': 47.408586863663956, 'west': 8.589968123394014, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>['eam']</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>238</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>lg energy solution derichebourg</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>{'east': 2.3376845881749038, 'south': 49.14977227170855, 'north': 49.16534972829145, 'west': 2.313861411825096, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>239</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>hydrovolt</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>{'east': 11.002868481159044, 'south': 59.180746571333344, 'north': 59.255453428666655, 'west': 10.856731518840956, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>['recycling']</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>240</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
           <t>green cell</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>Świętokrzyskie</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>{'east': 20.84852492504332, 'south': 50.5355329482598, 'north': 50.553520245762655, 'west': 20.820214393804335, 'accuracyLevel': 1}</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
         <is>
           <t>['module_pack']</t>
         </is>

--- a/reconcile/storage/output/facilities.xlsx
+++ b/reconcile/storage/output/facilities.xlsx
@@ -8517,7 +8517,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>['recycling' 'cell']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>['cell' nan 'recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>['cell' nan 'recycling']</t>
+          <t>['cell' nan]</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>['recycling' 'cell']</t>
+          <t>['cell']</t>
         </is>
       </c>
     </row>
